--- a/Frameworks/MiniExcel/ExportCreateExcel/StronglyTypedExport.xlsx
+++ b/Frameworks/MiniExcel/ExportCreateExcel/StronglyTypedExport.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="Rb2360fc24aa34c76a7e563fdcdac3a2e"/>
+    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="R262ddf01849b49638f5acb3d8f6ae1cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -127,14 +127,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:F3"/>
+  <x:dimension ref="A1:E3"/>
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="18" customWidth="1"/>
     <x:col min="3" max="3" width="28" customWidth="1"/>
     <x:col min="4" max="4" width="14" customWidth="1"/>
     <x:col min="5" max="5" width="14" customWidth="1"/>
-    <x:col min="6" max="6" width="24" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -153,9 +152,6 @@
       <x:c r="E1" t="str" s="1">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="F1" t="str" s="1">
-        <x:v>PaidAt</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str" s="2">
@@ -172,9 +168,6 @@
       </x:c>
       <x:c r="E2" t="str" s="2">
         <x:v>USD</x:v>
-      </x:c>
-      <x:c r="F2" s="5">
-        <x:v>46091.395833333336</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -193,12 +186,9 @@
       <x:c r="E3" t="str" s="2">
         <x:v>CNY</x:v>
       </x:c>
-      <x:c r="F3" s="5">
-        <x:v>46092.59375</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F3"/>
+  <x:autoFilter ref="A1:E3"/>
   <x:drawing r:id="drawing1"/>
 </x:worksheet>
 </file>